--- a/data/file_generation/reference/data_205/成交区间_res.xlsx
+++ b/data/file_generation/reference/data_205/成交区间_res.xlsx
@@ -10804,18 +10804,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4F24289-942A-44E4-8DA0-8F07C69337EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D518D85F-E2E3-4E2E-8442-40A058421393}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F715B237-9360-4B7F-8D29-52298D947399}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B748D05D-354A-4C1F-87F6-1D48D6F00C65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{369562FA-A49E-417E-852D-46AC2BA5FB6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C99CCC06-CDCC-47D8-BBC9-8B4F68C954F5}"/>
 </file>